--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/updateAdmin-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/user-controller/updateAdmin-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="158">
-  <si>
-    <t>Statement: user-controller.updateAdmin(adminId, data) – Server Action. Validates UpdateAdminInput (all optional). Delegates to userService.updateAdmin(). Returns ActionResult&lt;AdminWithUser&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="139">
+  <si>
+    <t>Statement: updateAdmin(id, data) – Validates the update-admin input and returns an ActionResult&lt;MemberWithUser&gt;. Returns success with the updated admin on success. Returns a field-level validation error for schema failures without calling the service. Returns a failure with the service error message for NotFoundError and TransactionError.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: adminId: string, data: UpdateAdminInput (all optional)</t>
+    <t>Input: id: string, data: UpdateAdminInput { email?, fullName?, phone?, dateOfBirth?, password? }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>userService.updateAdmin is mock-injected</t>
+    <t>The admin store may be empty or populated. All fields in UpdateAdminInput are optional. When a field is present, it must pass the same format and length rules as in createAdmin. When a field is undefined, it is ignored and the update proceeds.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;AdminWithUser&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;MemberWithUser&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: updated AdminWithUser returned. On validation failure: errors returned. On AppError: message returned.</t>
+    <t>On success: admin updated successfully, returned data reflects the applied changes. On validation failure: field-level validation error returned, the service is not called. On service error: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,55 +64,22 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>all fields valid</t>
-  </si>
-  <si>
-    <t>optional fields pass schema</t>
-  </si>
-  <si>
-    <t>fullName optional</t>
-  </si>
-  <si>
-    <t>fullName ≥ 8 chars if provided</t>
-  </si>
-  <si>
-    <t>fullName &lt; 8 chars → validation error</t>
-  </si>
-  <si>
-    <t>email optional</t>
-  </si>
-  <si>
-    <t>valid email if provided</t>
-  </si>
-  <si>
-    <t>invalid email → validation error</t>
-  </si>
-  <si>
-    <t>password optional</t>
-  </si>
-  <si>
-    <t>password ≥ 8 chars, upper+digit+special</t>
-  </si>
-  <si>
-    <t>password &lt; 8 chars → validation error</t>
-  </si>
-  <si>
-    <t>password missing digit → validation error</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves updated AdminWithUser</t>
-  </si>
-  <si>
-    <t>throws NotFoundError → failure</t>
-  </si>
-  <si>
-    <t>throws ConflictError → failure</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>Input validity</t>
+  </si>
+  <si>
+    <t>Valid partial input ({ fullName: "Admin Updated" }), matching admin exists → admin updated successfully, returned fullName matches the new value</t>
+  </si>
+  <si>
+    <t>ID existence</t>
+  </si>
+  <si>
+    <t>Non-existent id, no matching record exists (NotFoundError) → operation fails with the returned error message</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>A database transaction failure occurs (TransactionError) → operation fails with the returned error message</t>
   </si>
   <si>
     <t>No TC</t>
@@ -130,106 +97,34 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,2,4,6,9</t>
-  </si>
-  <si>
-    <t>{ fullName: "Admin Updated Name" }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }</t>
-  </si>
-  <si>
-    <t>1,9</t>
-  </si>
-  <si>
-    <t>{} (empty object), service resolves</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ fullName: "JohnDo" } (7 chars)</t>
-  </si>
-  <si>
-    <t>{ success: false, errors defined }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>{ fullName: "John Doe" } (8 chars)</t>
-  </si>
-  <si>
-    <t>{ success: true } (boundary valid)</t>
-  </si>
-  <si>
-    <t>{ fullName: "A".repeat(64) } (64 chars)</t>
-  </si>
-  <si>
-    <t>{ fullName: "A".repeat(65) } (65 chars)</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ email: "bademail" }</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>{ password: "Sec1!ab" } (7 chars)</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>{ password: "Secure1!" } (8 chars)</t>
-  </si>
-  <si>
-    <t>{ success: true } (password boundary valid)</t>
-  </si>
-  <si>
-    <t>{ password: "Secure1!" + "a".repeat(56) } (64 chars)</t>
-  </si>
-  <si>
-    <t>{ success: true } (password upper boundary)</t>
-  </si>
-  <si>
-    <t>{ password: "Secure1!" + "a".repeat(57) } (65 chars)</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>{ password: "SecurePass!" } (missing digit)</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>valid update, service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Admin not found" }</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>valid update, service throws ConflictError</t>
-  </si>
-  <si>
-    <t>{ success: false, message from error }</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>valid update, service throws Error</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { fullName: "Admin Updated" }, admin exists and is updated successfully</t>
+  </si>
+  <si>
+    <t>admin updated successfully, returned data fullName is "Admin Updated"</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>non-existent id, data: { fullName: "Admin Updated" }, no matching record exists (NotFoundError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "Not found"</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { fullName: "Admin Updated" }, database transaction failure occurs (TransactionError)</t>
+  </si>
+  <si>
+    <t>operation fails with message "DB Error"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -238,85 +133,208 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>fullName length</t>
-  </si>
-  <si>
-    <t>fullName 7 → invalid; 8 → valid (min); 64 → valid (max); 65 → invalid</t>
-  </si>
-  <si>
-    <t>password length</t>
-  </si>
-  <si>
-    <t>password 7 → invalid; 8 → valid (min); 64 → valid (max); 65 → invalid</t>
-  </si>
-  <si>
-    <t>password complexity</t>
-  </si>
-  <si>
-    <t>missing digit → invalid; missing uppercase → invalid; missing special → invalid</t>
+    <t>id boundary</t>
+  </si>
+  <si>
+    <t>id: "" (empty string, length 0): no record can match → operation fails</t>
+  </si>
+  <si>
+    <t>id: "a" (one character), no matching record exists → operation fails</t>
+  </si>
+  <si>
+    <t>id: "a" (one character), matching record exists → admin updated successfully</t>
+  </si>
+  <si>
+    <t>email presence</t>
+  </si>
+  <si>
+    <t>email: undefined (field omitted) → update proceeds successfully, email not changed</t>
+  </si>
+  <si>
+    <t>email: "" (empty string) → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>email: "a" (one character, invalid format) → validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>fullName presence</t>
+  </si>
+  <si>
+    <t>fullName: undefined (field omitted) → update proceeds successfully, fullName not changed</t>
+  </si>
+  <si>
+    <t>fullName: "" (empty string) → validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>fullName: "a" (one character, below minimum) → validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>phone presence</t>
+  </si>
+  <si>
+    <t>phone: undefined (field omitted) → update proceeds successfully, phone not changed</t>
+  </si>
+  <si>
+    <t>phone: "" (empty string) → validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>phone: "a" (one character, invalid format) → validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>dateOfBirth presence</t>
+  </si>
+  <si>
+    <t>dateOfBirth: undefined (field omitted) → update proceeds successfully, dateOfBirth not changed</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "" (empty string) → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>dateOfBirth: "a" (one character, invalid format) → validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>password presence</t>
+  </si>
+  <si>
+    <t>password: undefined (field omitted) → update proceeds successfully, password not changed</t>
+  </si>
+  <si>
+    <t>password: "" (empty string) → validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>password: "a" (one character, fails all rules) → validation fails: password field error returned</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>fullName=7</t>
-  </si>
-  <si>
-    <t>{ fullName: "JohnDo" }</t>
-  </si>
-  <si>
-    <t>success=false, errors defined</t>
-  </si>
-  <si>
-    <t>fullName=8</t>
-  </si>
-  <si>
-    <t>{ fullName: "John Doe" }</t>
-  </si>
-  <si>
-    <t>schema passes</t>
-  </si>
-  <si>
-    <t>fullName=64</t>
-  </si>
-  <si>
-    <t>{ fullName: "A".repeat(64) }</t>
-  </si>
-  <si>
-    <t>fullName=65</t>
-  </si>
-  <si>
-    <t>{ fullName: "A".repeat(65) }</t>
-  </si>
-  <si>
-    <t>password=7</t>
-  </si>
-  <si>
-    <t>{ password: "Sec1!ab" }</t>
-  </si>
-  <si>
-    <t>password=8</t>
-  </si>
-  <si>
-    <t>{ password: "Secure1!" }</t>
-  </si>
-  <si>
-    <t>password=64</t>
-  </si>
-  <si>
-    <t>{ password: "Secure1!" + "a".repeat(56) }</t>
-  </si>
-  <si>
-    <t>password=65</t>
-  </si>
-  <si>
-    <t>{ password: "Secure1!" + "a".repeat(57) }</t>
-  </si>
-  <si>
-    <t>no digit</t>
-  </si>
-  <si>
-    <t>{ password: "SecurePass!" }</t>
+    <t>BVA-1  (id="")</t>
+  </si>
+  <si>
+    <t>id: "", data: { fullName: "Admin Updated" }, no record can match an empty id</t>
+  </si>
+  <si>
+    <t>BVA-2  (id="a", no match)</t>
+  </si>
+  <si>
+    <t>id: "a", data: { fullName: "Admin Updated" }, no admin exists with id "a"</t>
+  </si>
+  <si>
+    <t>BVA-3  (id="a", match)</t>
+  </si>
+  <si>
+    <t>id: "a", data: { fullName: "Admin Updated" }, an admin with id "a" exists in the store</t>
+  </si>
+  <si>
+    <t>admin updated successfully, returned data id is "a"</t>
+  </si>
+  <si>
+    <t>BVA-4  (email=undefined)</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { email: undefined }</t>
+  </si>
+  <si>
+    <t>admin updated successfully</t>
+  </si>
+  <si>
+    <t>BVA-5  (email="")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { email: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: email field error returned</t>
+  </si>
+  <si>
+    <t>BVA-6  (email="a")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { email: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-7  (fullName=undefined)</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { fullName: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-8  (fullName="")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { fullName: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: fullName field error returned</t>
+  </si>
+  <si>
+    <t>BVA-9  (fullName="a")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { fullName: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-10 (phone=undefined)</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { phone: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-11 (phone="")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { phone: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: phone field error returned</t>
+  </si>
+  <si>
+    <t>BVA-12 (phone="a")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { phone: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-13 (dob=undefined)</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { dateOfBirth: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-14 (dob="")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { dateOfBirth: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: dateOfBirth field error returned</t>
+  </si>
+  <si>
+    <t>BVA-15 (dob="a")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { dateOfBirth: "a" }</t>
+  </si>
+  <si>
+    <t>BVA-16 (password=undefined)</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { password: undefined }</t>
+  </si>
+  <si>
+    <t>BVA-17 (password="")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { password: "" }</t>
+  </si>
+  <si>
+    <t>validation fails: password field error returned</t>
+  </si>
+  <si>
+    <t>BVA-18 (password="a")</t>
+  </si>
+  <si>
+    <t>known existing admin id, data: { password: "a" }</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -325,130 +343,58 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>Valid fullName update</t>
-  </si>
-  <si>
-    <t>success=true</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>Empty object</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>fullName 7 chars</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
     <t>BVA-2</t>
   </si>
   <si>
-    <t>fullName 8 chars</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
     <t>BVA-3</t>
   </si>
   <si>
-    <t>fullName 64 chars</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
     <t>BVA-4</t>
   </si>
   <si>
-    <t>fullName 65 chars</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Invalid email</t>
-  </si>
-  <si>
-    <t>EP-8</t>
-  </si>
-  <si>
     <t>BVA-5</t>
   </si>
   <si>
-    <t>password 7 chars</t>
-  </si>
-  <si>
-    <t>EP-9</t>
-  </si>
-  <si>
     <t>BVA-6</t>
   </si>
   <si>
-    <t>password 8 chars</t>
-  </si>
-  <si>
-    <t>EP-10</t>
-  </si>
-  <si>
     <t>BVA-7</t>
   </si>
   <si>
-    <t>password 64 chars</t>
-  </si>
-  <si>
-    <t>EP-11</t>
-  </si>
-  <si>
     <t>BVA-8</t>
   </si>
   <si>
-    <t>password 65 chars</t>
-  </si>
-  <si>
-    <t>EP-12</t>
-  </si>
-  <si>
     <t>BVA-9</t>
   </si>
   <si>
-    <t>password missing digit</t>
-  </si>
-  <si>
-    <t>EP-13</t>
-  </si>
-  <si>
-    <t>Service throws NotFoundError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-14</t>
-  </si>
-  <si>
-    <t>Service throws ConflictError</t>
-  </si>
-  <si>
-    <t>EP-15</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, "An unexpected error occurred"</t>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
+  </si>
+  <si>
+    <t>BVA-17</t>
+  </si>
+  <si>
+    <t>BVA-18</t>
   </si>
   <si>
     <t>Testing</t>
@@ -481,16 +427,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>AUTH-06</t>
+    <t>CTRL-10</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +949,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1050,10 +993,10 @@
         <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -1061,139 +1004,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1204,7 +1021,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1216,19 +1033,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1236,16 +1053,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1253,16 +1070,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1270,220 +1087,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1494,7 +1107,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1504,13 +1117,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1518,10 +1131,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1529,10 +1142,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>75</v>
+        <v>38</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1540,10 +1153,175 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>77</v>
+        <v>38</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>78</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1554,7 +1332,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1566,19 +1344,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1586,16 +1364,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1603,16 +1381,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1620,16 +1398,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1637,16 +1415,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1654,16 +1432,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1671,16 +1449,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1688,16 +1466,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1705,16 +1483,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,16 +1500,169 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>82</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1742,7 +1673,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1755,22 +1686,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1778,19 +1709,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1798,19 +1729,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>106</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1818,19 +1749,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>107</v>
+        <v>33</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>82</v>
+        <v>35</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1838,19 +1769,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1858,19 +1789,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>115</v>
+        <v>66</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1878,19 +1809,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>116</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1898,19 +1829,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1</v>
+        <v>111</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1918,19 +1849,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>121</v>
+        <v>1</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>123</v>
+        <v>74</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1938,19 +1869,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>124</v>
+        <v>1</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>126</v>
+        <v>77</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,19 +1889,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>127</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1978,19 +1909,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>130</v>
+        <v>1</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1998,19 +1929,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>133</v>
+        <v>1</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>135</v>
+        <v>84</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>82</v>
+        <v>29</v>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2018,19 +1949,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>136</v>
+        <v>1</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>138</v>
+        <v>72</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2038,19 +1969,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>139</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1</v>
+        <v>118</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>138</v>
+        <v>89</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -2058,19 +1989,139 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>141</v>
+        <v>1</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1</v>
+        <v>119</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>142</v>
+        <v>91</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>143</v>
+        <v>89</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>143</v>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2098,16 +2149,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -2115,45 +2166,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>154</v>
+      <c r="A3" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="B3" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C3" s="1">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -2162,19 +2213,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>157</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
